--- a/data/trans_orig/P07-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P07-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su salud general autopercibida en 2007</t>
+          <t>Población según su salud general autopercibida en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>42683</t>
+          <t>42057</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>72043</t>
+          <t>70818</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>123297</t>
+          <t>122332</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>170104</t>
+          <t>167300</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>174159</t>
+          <t>175244</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>224579</t>
+          <t>228159</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,72%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>248336</t>
+          <t>248069</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>304071</t>
+          <t>302509</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>469805</t>
+          <t>475399</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>539985</t>
+          <t>546692</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>737388</t>
+          <t>740130</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>826576</t>
+          <t>832759</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>35,48%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>405856</t>
+          <t>407466</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>468959</t>
+          <t>470238</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>428792</t>
+          <t>427435</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>497059</t>
+          <t>499366</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>857095</t>
+          <t>858199</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>951340</t>
+          <t>947924</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>40,39%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>178922</t>
+          <t>177278</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>233410</t>
+          <t>229309</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>130296</t>
+          <t>131941</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>174760</t>
+          <t>174448</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>320898</t>
+          <t>322800</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>387842</t>
+          <t>388372</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,55%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>43411</t>
+          <t>42325</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>73617</t>
+          <t>72590</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>35893</t>
+          <t>35082</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>63397</t>
+          <t>60716</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>86165</t>
+          <t>85026</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>124867</t>
+          <t>124527</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9208</t>
+          <t>9078</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23828</t>
+          <t>24694</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29922</t>
+          <t>30264</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>54955</t>
+          <t>55861</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>44598</t>
+          <t>42762</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>72980</t>
+          <t>72450</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>98809</t>
+          <t>99040</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>141662</t>
+          <t>141574</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>182400</t>
+          <t>181170</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>235395</t>
+          <t>234657</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>291918</t>
+          <t>293004</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>362238</t>
+          <t>360811</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,0%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536250</t>
+          <t>537035</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>612516</t>
+          <t>618696</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>670252</t>
+          <t>673283</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>750638</t>
+          <t>754298</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>42,41%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1230523</t>
+          <t>1235486</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1340781</t>
+          <t>1342912</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>40,94%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>725991</t>
+          <t>725264</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>807829</t>
+          <t>808269</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>47,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>441746</t>
+          <t>443014</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>514879</t>
+          <t>514330</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1190851</t>
+          <t>1187395</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1300828</t>
+          <t>1297292</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>39,55%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>187329</t>
+          <t>189733</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>245956</t>
+          <t>244866</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>129587</t>
+          <t>128749</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>170921</t>
+          <t>173009</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>330735</t>
+          <t>333484</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>403510</t>
+          <t>405737</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,37%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4446</t>
+          <t>4522</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18835</t>
+          <t>18715</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4505</t>
+          <t>5027</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17609</t>
+          <t>17152</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11902</t>
+          <t>11032</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31545</t>
+          <t>29781</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>25953</t>
+          <t>24851</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>51728</t>
+          <t>49854</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>44818</t>
+          <t>45911</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>75052</t>
+          <t>75410</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>77532</t>
+          <t>76435</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>117958</t>
+          <t>115079</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,2%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>170545</t>
+          <t>170420</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>217319</t>
+          <t>216993</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>173414</t>
+          <t>174096</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>217053</t>
+          <t>217564</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>358335</t>
+          <t>357297</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>422716</t>
+          <t>420882</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>40,95%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>200318</t>
+          <t>201963</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>248421</t>
+          <t>248394</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>131535</t>
+          <t>130317</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>175178</t>
+          <t>172015</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>340815</t>
+          <t>343394</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>405525</t>
+          <t>405406</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,44%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>69920</t>
+          <t>71156</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>105577</t>
+          <t>106679</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>47487</t>
+          <t>47696</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>77695</t>
+          <t>78371</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>126815</t>
+          <t>124934</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>173256</t>
+          <t>172242</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,76%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>65200</t>
+          <t>65555</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>98792</t>
+          <t>100673</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>169844</t>
+          <t>168540</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>222364</t>
+          <t>223963</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>245852</t>
+          <t>244314</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>309821</t>
+          <t>308535</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>394920</t>
+          <t>395416</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>472126</t>
+          <t>469415</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>717831</t>
+          <t>724357</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>816921</t>
+          <t>825377</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1145824</t>
+          <t>1149422</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1269087</t>
+          <t>1264869</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,01%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1155659</t>
+          <t>1159061</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1262316</t>
+          <t>1271312</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1311918</t>
+          <t>1315480</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1422408</t>
+          <t>1434115</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2495830</t>
+          <t>2495734</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2659690</t>
+          <t>2659599</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,7 +3090,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1138410</t>
+          <t>1140496</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1251695</t>
+          <t>1245941</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>731544</t>
+          <t>734063</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>830964</t>
+          <t>826890</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1897226</t>
+          <t>1899312</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2054271</t>
+          <t>2047057</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,76%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>321219</t>
+          <t>321298</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>396703</t>
+          <t>397844</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>230790</t>
+          <t>230193</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>292755</t>
+          <t>293791</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>572784</t>
+          <t>571076</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>666791</t>
+          <t>667699</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,03%</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su salud general autopercibida en 2012</t>
+          <t>Población según su salud general autopercibida en 2012 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>55971</t>
+          <t>57993</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>89645</t>
+          <t>92656</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>130441</t>
+          <t>129921</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>176242</t>
+          <t>178042</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>197100</t>
+          <t>200076</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>254157</t>
+          <t>258847</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,2%</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>240349</t>
+          <t>239357</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>295682</t>
+          <t>297722</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>438034</t>
+          <t>437509</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>509478</t>
+          <t>507810</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>696190</t>
+          <t>696359</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>784515</t>
+          <t>789222</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>34,14%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>393831</t>
+          <t>395787</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>458465</t>
+          <t>461400</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>47,34%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>495093</t>
+          <t>498913</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>565608</t>
+          <t>573818</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>911502</t>
+          <t>916394</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1013103</t>
+          <t>1008039</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>43,61%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>141009</t>
+          <t>140646</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>189692</t>
+          <t>188773</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>134162</t>
+          <t>133229</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>183090</t>
+          <t>184462</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>287418</t>
+          <t>285735</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>353324</t>
+          <t>358861</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,53%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>29541</t>
+          <t>30248</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>54799</t>
+          <t>56062</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12632</t>
+          <t>11609</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>31370</t>
+          <t>31006</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>47532</t>
+          <t>47393</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>81076</t>
+          <t>78716</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14605</t>
+          <t>14914</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34161</t>
+          <t>36317</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31849</t>
+          <t>31112</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59296</t>
+          <t>58165</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>50076</t>
+          <t>51066</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>84662</t>
+          <t>85806</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>152614</t>
+          <t>150773</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>203062</t>
+          <t>202941</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>211106</t>
+          <t>210309</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>269985</t>
+          <t>270717</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>380545</t>
+          <t>374796</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>455641</t>
+          <t>454678</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,24%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>770809</t>
+          <t>764935</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>860784</t>
+          <t>858996</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>767820</t>
+          <t>767195</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>850119</t>
+          <t>853465</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>48,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1560714</t>
+          <t>1561469</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1687360</t>
+          <t>1687199</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>45,43%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>615911</t>
+          <t>616762</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>706133</t>
+          <t>701602</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>459634</t>
+          <t>455366</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>536589</t>
+          <t>540269</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1101861</t>
+          <t>1097002</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1211463</t>
+          <t>1214706</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,71%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>256877</t>
+          <t>257454</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>318316</t>
+          <t>319401</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>142409</t>
+          <t>142388</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>189911</t>
+          <t>193539</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>415883</t>
+          <t>415725</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>496596</t>
+          <t>495048</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,33%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1891</t>
+          <t>1082</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13541</t>
+          <t>13315</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>1159</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13102</t>
+          <t>12008</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4927</t>
+          <t>4428</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21433</t>
+          <t>20174</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14934</t>
+          <t>14596</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>38840</t>
+          <t>37782</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19870</t>
+          <t>20761</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>42965</t>
+          <t>44015</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>40871</t>
+          <t>38971</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>73112</t>
+          <t>71243</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,6%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>160250</t>
+          <t>159855</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>203932</t>
+          <t>202596</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>42,27%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>203056</t>
+          <t>202112</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>249868</t>
+          <t>247159</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>54,01%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>374526</t>
+          <t>374840</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>440749</t>
+          <t>438559</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>46,81%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>174387</t>
+          <t>178208</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>221482</t>
+          <t>224057</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>125041</t>
+          <t>127044</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>166142</t>
+          <t>168789</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>317088</t>
+          <t>315130</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>375880</t>
+          <t>377994</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>40,35%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>55211</t>
+          <t>54162</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>88622</t>
+          <t>90824</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>37841</t>
+          <t>38439</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>65503</t>
+          <t>65777</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>100488</t>
+          <t>98690</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>143406</t>
+          <t>144957</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,47%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>80761</t>
+          <t>81937</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>123868</t>
+          <t>123876</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5753,7 +5753,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>174529</t>
+          <t>174513</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>231469</t>
+          <t>230319</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>270920</t>
+          <t>267406</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>340511</t>
+          <t>339998</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>426390</t>
+          <t>423766</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>510216</t>
+          <t>509059</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>697002</t>
+          <t>695421</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>794201</t>
+          <t>796332</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1149092</t>
+          <t>1151428</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1280057</t>
+          <t>1278343</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,36%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1365647</t>
+          <t>1367373</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1482164</t>
+          <t>1484517</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1506567</t>
+          <t>1508202</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1628859</t>
+          <t>1629523</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>45,91%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2903622</t>
+          <t>2907389</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3072733</t>
+          <t>3083342</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>44,29%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>965565</t>
+          <t>963952</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1074604</t>
+          <t>1073221</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>757739</t>
+          <t>745666</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>860377</t>
+          <t>848253</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1739979</t>
+          <t>1741020</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1897680</t>
+          <t>1897454</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,25%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>359909</t>
+          <t>362875</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>437176</t>
+          <t>439894</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>206490</t>
+          <t>206739</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>267137</t>
+          <t>268865</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6245,7 +6245,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>585941</t>
+          <t>588034</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>689237</t>
+          <t>687296</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,87%</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6456,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su salud general autopercibida en 2016</t>
+          <t>Población según su salud general autopercibida en 2016 (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6651,12 +6651,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>37992</t>
+          <t>37301</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>63281</t>
+          <t>64291</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>94566</t>
+          <t>95127</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>138221</t>
+          <t>137775</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>141572</t>
+          <t>141141</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>192246</t>
+          <t>192029</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,01%</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>176550</t>
+          <t>176133</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>222859</t>
+          <t>224244</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>304853</t>
+          <t>305502</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>370106</t>
+          <t>370616</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>497145</t>
+          <t>497290</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>579378</t>
+          <t>575735</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>33,0%</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>250848</t>
+          <t>250810</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>302499</t>
+          <t>301526</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>293235</t>
+          <t>294729</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>355981</t>
+          <t>354922</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>564311</t>
+          <t>563683</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>644704</t>
+          <t>643274</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>36,87%</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>142117</t>
+          <t>140996</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>187993</t>
+          <t>187778</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>138940</t>
+          <t>137596</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>183378</t>
+          <t>185952</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7040,12 +7040,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>292595</t>
+          <t>290573</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>356703</t>
+          <t>354582</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,32%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>51787</t>
+          <t>52089</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>81801</t>
+          <t>82376</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>39542</t>
+          <t>40202</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>69142</t>
+          <t>68382</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>97750</t>
+          <t>96984</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>139654</t>
+          <t>139818</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,01%</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24419</t>
+          <t>24064</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50192</t>
+          <t>49297</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7348,12 +7348,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>50938</t>
+          <t>50251</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>82624</t>
+          <t>83600</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>79251</t>
+          <t>82085</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>122983</t>
+          <t>123738</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>189751</t>
+          <t>189870</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>245164</t>
+          <t>246665</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>244937</t>
+          <t>242135</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>305522</t>
+          <t>307985</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>447220</t>
+          <t>444722</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>528007</t>
+          <t>532998</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,12%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>585945</t>
+          <t>591265</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>678107</t>
+          <t>675206</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>576407</t>
+          <t>577100</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>656598</t>
+          <t>658633</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1194074</t>
+          <t>1189105</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1311432</t>
+          <t>1310148</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,25%</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>754781</t>
+          <t>754063</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>843973</t>
+          <t>841223</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>655641</t>
+          <t>650800</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>738174</t>
+          <t>737950</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1438760</t>
+          <t>1430904</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1557727</t>
+          <t>1560372</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>38,41%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>361655</t>
+          <t>358152</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>434217</t>
+          <t>427569</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>305408</t>
+          <t>305171</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>369643</t>
+          <t>370362</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>680102</t>
+          <t>678152</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>774356</t>
+          <t>772030</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,0%</t>
         </is>
       </c>
     </row>
@@ -8015,12 +8015,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1920</t>
+          <t>1948</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13533</t>
+          <t>12711</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8030,12 +8030,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3913</t>
+          <t>4421</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18492</t>
+          <t>17848</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8243</t>
+          <t>8094</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25639</t>
+          <t>25304</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16075</t>
+          <t>17203</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>36933</t>
+          <t>38824</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>32329</t>
+          <t>32294</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>58131</t>
+          <t>60637</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>55151</t>
+          <t>54948</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>90776</t>
+          <t>88475</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,1%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>126755</t>
+          <t>126277</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>168241</t>
+          <t>168307</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>158666</t>
+          <t>158950</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>203518</t>
+          <t>205258</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>297035</t>
+          <t>299862</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>359486</t>
+          <t>364051</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>33,34%</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>214343</t>
+          <t>214313</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>261587</t>
+          <t>264634</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8369,12 +8369,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>48,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>194749</t>
+          <t>194763</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>239484</t>
+          <t>240296</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8409,7 +8409,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>422217</t>
+          <t>421011</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>491123</t>
+          <t>485516</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>44,46%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +8467,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>107644</t>
+          <t>109326</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>149244</t>
+          <t>151093</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8482,12 +8482,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>77947</t>
+          <t>76289</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>112667</t>
+          <t>111089</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8537,12 +8537,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>197711</t>
+          <t>196369</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>251293</t>
+          <t>250921</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8552,12 +8552,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,98%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>74581</t>
+          <t>73280</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>111730</t>
+          <t>111659</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8712,7 +8712,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>163818</t>
+          <t>163663</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>221386</t>
+          <t>221466</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>248123</t>
+          <t>248438</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>314900</t>
+          <t>319120</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>404893</t>
+          <t>405120</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>485232</t>
+          <t>480651</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>604566</t>
+          <t>607513</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>705184</t>
+          <t>704058</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1034114</t>
+          <t>1037517</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1157627</t>
+          <t>1157690</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,7 +8895,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1002718</t>
+          <t>1004425</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1108317</t>
+          <t>1111582</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1064627</t>
+          <t>1066829</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1180086</t>
+          <t>1184544</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2103454</t>
+          <t>2104028</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2257631</t>
+          <t>2264844</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9013,7 +9013,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,83%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1142311</t>
+          <t>1149977</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1258458</t>
+          <t>1259612</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1020635</t>
+          <t>1022064</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1132472</t>
+          <t>1128602</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9086,12 +9086,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2200981</t>
+          <t>2193749</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2356774</t>
+          <t>2352482</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,1%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>540164</t>
+          <t>545180</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>630997</t>
+          <t>633892</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>445682</t>
+          <t>444231</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>524088</t>
+          <t>527394</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1007257</t>
+          <t>1009816</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1130622</t>
+          <t>1127075</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,34%</t>
         </is>
       </c>
     </row>
@@ -9415,7 +9415,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su salud general autopercibida en 2023</t>
+          <t>Población según su salud general autopercibida en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9610,12 +9610,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>44305</t>
+          <t>44684</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>68886</t>
+          <t>69762</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9625,12 +9625,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9645,12 +9645,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>103543</t>
+          <t>106371</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>132981</t>
+          <t>135653</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9660,12 +9660,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9680,12 +9680,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>156016</t>
+          <t>155154</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>195574</t>
+          <t>193083</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9695,12 +9695,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,2%</t>
         </is>
       </c>
     </row>
@@ -9723,12 +9723,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>130876</t>
+          <t>131906</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>169223</t>
+          <t>169119</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9738,12 +9738,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9758,12 +9758,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>256497</t>
+          <t>254181</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>294959</t>
+          <t>295244</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9773,12 +9773,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>39,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9793,12 +9793,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>397197</t>
+          <t>396390</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>451334</t>
+          <t>453292</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9808,12 +9808,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,68%</t>
         </is>
       </c>
     </row>
@@ -9836,12 +9836,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>187279</t>
+          <t>184629</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>227323</t>
+          <t>225578</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9851,12 +9851,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9871,12 +9871,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>255124</t>
+          <t>254647</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>295015</t>
+          <t>296428</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9886,12 +9886,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9906,12 +9906,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>452406</t>
+          <t>452034</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>512113</t>
+          <t>512239</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9921,12 +9921,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>40,32%</t>
         </is>
       </c>
     </row>
@@ -9949,12 +9949,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55827</t>
+          <t>55558</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>88993</t>
+          <t>87597</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9964,12 +9964,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9984,12 +9984,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>56270</t>
+          <t>56272</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>82107</t>
+          <t>82293</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10019,12 +10019,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>118817</t>
+          <t>120719</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>159316</t>
+          <t>161449</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,71%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>24084</t>
+          <t>25216</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>46384</t>
+          <t>48725</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10997</t>
+          <t>10766</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>29184</t>
+          <t>29267</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>38322</t>
+          <t>38995</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>67693</t>
+          <t>68782</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -10292,12 +10292,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34098</t>
+          <t>32971</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>65553</t>
+          <t>64452</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10307,12 +10307,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10327,12 +10327,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36114</t>
+          <t>37389</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>64808</t>
+          <t>65007</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10342,7 +10342,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -10362,12 +10362,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>79017</t>
+          <t>78499</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>121501</t>
+          <t>121682</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10377,12 +10377,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -10405,12 +10405,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>173711</t>
+          <t>169363</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>291412</t>
+          <t>291379</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10420,7 +10420,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -10440,12 +10440,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>222713</t>
+          <t>221720</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>353348</t>
+          <t>351515</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10455,12 +10455,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10475,12 +10475,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>434436</t>
+          <t>447225</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>623522</t>
+          <t>621831</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10490,12 +10490,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,73%</t>
         </is>
       </c>
     </row>
@@ -10518,12 +10518,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>908645</t>
+          <t>906718</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1454622</t>
+          <t>1477528</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>63,51%</t>
+          <t>64,51%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10553,12 +10553,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1001162</t>
+          <t>999377</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1443807</t>
+          <t>1431625</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10588,12 +10588,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1960924</t>
+          <t>1961961</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2726267</t>
+          <t>2692805</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>43,33%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>59,47%</t>
         </is>
       </c>
     </row>
@@ -10631,12 +10631,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>456216</t>
+          <t>431213</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>754679</t>
+          <t>750965</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10646,12 +10646,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10666,12 +10666,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>406086</t>
+          <t>416143</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>630319</t>
+          <t>636028</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10701,12 +10701,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>953419</t>
+          <t>956603</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1348600</t>
+          <t>1344889</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,7%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>184498</t>
+          <t>188442</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>327463</t>
+          <t>332447</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>131587</t>
+          <t>135096</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>291686</t>
+          <t>284268</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>362044</t>
+          <t>358555</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>557927</t>
+          <t>559238</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,35%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4885</t>
+          <t>4698</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15876</t>
+          <t>16170</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6822</t>
+          <t>6635</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16766</t>
+          <t>16996</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13150</t>
+          <t>13267</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27039</t>
+          <t>27591</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>46091</t>
+          <t>46953</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>76453</t>
+          <t>75167</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>46896</t>
+          <t>46990</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>70150</t>
+          <t>71235</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>100426</t>
+          <t>102184</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>139572</t>
+          <t>139176</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,65%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>273689</t>
+          <t>274117</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>327521</t>
+          <t>330510</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>51,11%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>276327</t>
+          <t>273761</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>322900</t>
+          <t>320491</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>41,45%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>48,89%</t>
+          <t>48,53%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>565332</t>
+          <t>562733</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>633599</t>
+          <t>635692</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>43,05%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>48,63%</t>
         </is>
       </c>
     </row>
@@ -11313,12 +11313,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>162550</t>
+          <t>163594</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>211465</t>
+          <t>215077</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11328,12 +11328,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11348,12 +11348,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>188248</t>
+          <t>187388</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>232402</t>
+          <t>232894</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>363808</t>
+          <t>366587</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>431557</t>
+          <t>431321</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>33,0%</t>
         </is>
       </c>
     </row>
@@ -11426,12 +11426,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>70022</t>
+          <t>67974</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>120129</t>
+          <t>120986</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11441,12 +11441,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11461,12 +11461,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>67978</t>
+          <t>67727</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>101189</t>
+          <t>99571</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>144830</t>
+          <t>145802</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>206912</t>
+          <t>208928</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,98%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>85949</t>
+          <t>88683</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>135966</t>
+          <t>135490</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>147122</t>
+          <t>147492</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>203959</t>
+          <t>205888</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>255730</t>
+          <t>253720</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>331208</t>
+          <t>330065</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>357451</t>
+          <t>352489</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>510670</t>
+          <t>509755</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>512067</t>
+          <t>514274</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>692552</t>
+          <t>696138</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>957353</t>
+          <t>941589</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1185136</t>
+          <t>1174982</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,54%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1408025</t>
+          <t>1409485</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1974379</t>
+          <t>1984539</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>57,49%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1575876</t>
+          <t>1568373</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2105602</t>
+          <t>2082068</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>56,98%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3031962</t>
+          <t>3026002</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3766130</t>
+          <t>3790847</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>42,59%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>53,35%</t>
         </is>
       </c>
     </row>
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>715017</t>
+          <t>715138</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1011915</t>
+          <t>1007801</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12010,12 +12010,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12030,12 +12030,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>688205</t>
+          <t>667314</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>906901</t>
+          <t>913062</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12065,12 +12065,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1522796</t>
+          <t>1530731</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1880864</t>
+          <t>1885585</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,54%</t>
         </is>
       </c>
     </row>
@@ -12108,12 +12108,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>308169</t>
+          <t>305779</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>459506</t>
+          <t>460729</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12123,12 +12123,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>233238</t>
+          <t>232195</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>401929</t>
+          <t>397222</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12158,12 +12158,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12178,12 +12178,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>576113</t>
+          <t>591998</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>789624</t>
+          <t>805378</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12193,12 +12193,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,33%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P07-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P07-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>42057</t>
+          <t>42921</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>70818</t>
+          <t>69966</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>122332</t>
+          <t>121004</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>167300</t>
+          <t>167419</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>175244</t>
+          <t>175259</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>228159</t>
+          <t>230958</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,84%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>248069</t>
+          <t>250111</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>302509</t>
+          <t>304836</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>475399</t>
+          <t>471449</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>546692</t>
+          <t>540880</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>740130</t>
+          <t>741955</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>832759</t>
+          <t>825620</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>35,18%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>407466</t>
+          <t>408615</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>470238</t>
+          <t>467633</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>39,61%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>427435</t>
+          <t>430607</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>499366</t>
+          <t>500721</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>858199</t>
+          <t>855402</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>947924</t>
+          <t>947821</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>177278</t>
+          <t>181180</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>229309</t>
+          <t>231960</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>131941</t>
+          <t>129464</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>174448</t>
+          <t>175984</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>322800</t>
+          <t>324457</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>388372</t>
+          <t>391308</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,67%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>42325</t>
+          <t>43500</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>72590</t>
+          <t>73251</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>35082</t>
+          <t>34493</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>60716</t>
+          <t>63563</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>85026</t>
+          <t>85872</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>124527</t>
+          <t>127130</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9078</t>
+          <t>9386</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24694</t>
+          <t>24635</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30264</t>
+          <t>30214</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>55861</t>
+          <t>54602</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>42762</t>
+          <t>42859</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>72450</t>
+          <t>73469</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>99040</t>
+          <t>101359</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>141574</t>
+          <t>141435</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>181170</t>
+          <t>179091</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>234657</t>
+          <t>235408</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>360811</t>
+          <t>361143</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,01%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>537035</t>
+          <t>536438</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>618696</t>
+          <t>614105</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>673283</t>
+          <t>675317</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>754298</t>
+          <t>752766</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1235486</t>
+          <t>1230538</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1342912</t>
+          <t>1342866</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>725264</t>
+          <t>728365</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>808269</t>
+          <t>804656</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>47,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>443014</t>
+          <t>443023</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>514330</t>
+          <t>513214</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1187395</t>
+          <t>1187083</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1297292</t>
+          <t>1298786</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>39,6%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>189733</t>
+          <t>186742</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>244866</t>
+          <t>243420</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>128749</t>
+          <t>128792</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>173009</t>
+          <t>175697</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>333484</t>
+          <t>332297</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>405737</t>
+          <t>410886</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,53%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4522</t>
+          <t>4302</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18715</t>
+          <t>18407</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5027</t>
+          <t>5014</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17152</t>
+          <t>18965</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11032</t>
+          <t>11677</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29781</t>
+          <t>30580</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24851</t>
+          <t>25635</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>49854</t>
+          <t>50917</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>45911</t>
+          <t>45131</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>75410</t>
+          <t>74440</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>76435</t>
+          <t>77494</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>115079</t>
+          <t>115443</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,23%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>170420</t>
+          <t>172724</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>216993</t>
+          <t>218421</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>39,61%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>174096</t>
+          <t>175993</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>217564</t>
+          <t>218505</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>45,86%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>357297</t>
+          <t>357078</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>420882</t>
+          <t>421303</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>40,99%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>201963</t>
+          <t>201395</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>248394</t>
+          <t>246760</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>44,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>130317</t>
+          <t>130435</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>172015</t>
+          <t>170326</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>343394</t>
+          <t>343561</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>405406</t>
+          <t>407804</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>39,68%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>71156</t>
+          <t>69610</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>106679</t>
+          <t>103983</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>47696</t>
+          <t>47791</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>78371</t>
+          <t>76470</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>124934</t>
+          <t>127479</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>172242</t>
+          <t>172460</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,78%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>65555</t>
+          <t>65779</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>100673</t>
+          <t>103574</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>168540</t>
+          <t>169801</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>223963</t>
+          <t>226986</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>244314</t>
+          <t>244799</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>308535</t>
+          <t>305666</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>395416</t>
+          <t>394704</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>469415</t>
+          <t>472791</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>724357</t>
+          <t>725878</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>825377</t>
+          <t>822782</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1149422</t>
+          <t>1140536</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1264869</t>
+          <t>1267237</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,04%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1159061</t>
+          <t>1152088</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1271312</t>
+          <t>1261536</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1315480</t>
+          <t>1317358</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1434115</t>
+          <t>1426403</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2495734</t>
+          <t>2500443</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2659599</t>
+          <t>2656339</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>39,92%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1140496</t>
+          <t>1141091</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1245941</t>
+          <t>1258405</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>734063</t>
+          <t>731680</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>826890</t>
+          <t>831471</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1899312</t>
+          <t>1903555</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2047057</t>
+          <t>2050197</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,81%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>321298</t>
+          <t>325301</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>397844</t>
+          <t>398291</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>230193</t>
+          <t>232893</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>293791</t>
+          <t>292305</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>571076</t>
+          <t>572557</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>667699</t>
+          <t>671393</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,09%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>57993</t>
+          <t>57047</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>92656</t>
+          <t>92995</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>129921</t>
+          <t>130392</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>178042</t>
+          <t>175730</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>200076</t>
+          <t>196526</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>258847</t>
+          <t>255766</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,06%</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>239357</t>
+          <t>238965</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>297722</t>
+          <t>295650</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>437509</t>
+          <t>436100</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>507810</t>
+          <t>507189</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>696359</t>
+          <t>694444</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>789222</t>
+          <t>788965</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,13%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>395787</t>
+          <t>398549</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>461400</t>
+          <t>459930</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>40,89%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>498913</t>
+          <t>496989</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>573818</t>
+          <t>573676</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>916394</t>
+          <t>914352</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1008039</t>
+          <t>1014032</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>43,87%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>140646</t>
+          <t>141314</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>188773</t>
+          <t>190427</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>133229</t>
+          <t>135218</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>184462</t>
+          <t>183728</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>285735</t>
+          <t>287976</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>358861</t>
+          <t>354398</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,33%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>30248</t>
+          <t>31509</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>56062</t>
+          <t>55029</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11609</t>
+          <t>12271</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>31006</t>
+          <t>30324</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>47393</t>
+          <t>46444</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>78716</t>
+          <t>77510</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14914</t>
+          <t>14457</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36317</t>
+          <t>35521</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31112</t>
+          <t>30877</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58165</t>
+          <t>58790</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>51066</t>
+          <t>50969</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>85806</t>
+          <t>84026</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>150773</t>
+          <t>149174</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>202941</t>
+          <t>201672</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>210309</t>
+          <t>212009</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>270717</t>
+          <t>272480</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>374796</t>
+          <t>377599</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>454678</t>
+          <t>456151</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,28%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>764935</t>
+          <t>774865</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>858996</t>
+          <t>864981</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>767195</t>
+          <t>762279</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>853465</t>
+          <t>847760</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>43,44%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1561469</t>
+          <t>1563999</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1687199</t>
+          <t>1682661</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>45,31%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>616762</t>
+          <t>615194</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>701602</t>
+          <t>700023</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>455366</t>
+          <t>456969</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>540269</t>
+          <t>536654</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1097002</t>
+          <t>1099769</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1214706</t>
+          <t>1212876</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,66%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>257454</t>
+          <t>253263</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>319401</t>
+          <t>318836</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>142388</t>
+          <t>141548</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>193539</t>
+          <t>192842</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>415725</t>
+          <t>413604</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>495048</t>
+          <t>497014</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,38%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1082</t>
+          <t>1090</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13315</t>
+          <t>14323</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1159</t>
+          <t>1167</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12008</t>
+          <t>12581</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4428</t>
+          <t>4308</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20174</t>
+          <t>19301</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14596</t>
+          <t>13752</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37782</t>
+          <t>37752</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5184,7 +5184,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20761</t>
+          <t>19794</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>44015</t>
+          <t>42588</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>38971</t>
+          <t>39626</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>71243</t>
+          <t>73007</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,79%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>159855</t>
+          <t>159008</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>202596</t>
+          <t>206524</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>202112</t>
+          <t>203118</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>247159</t>
+          <t>248876</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>54,38%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>374840</t>
+          <t>375089</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>438559</t>
+          <t>439744</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>46,94%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>178208</t>
+          <t>177539</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>224057</t>
+          <t>222233</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>127044</t>
+          <t>125289</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>168789</t>
+          <t>168930</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>315130</t>
+          <t>313468</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>377994</t>
+          <t>375047</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>40,03%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>54162</t>
+          <t>53970</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>90824</t>
+          <t>88070</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>38439</t>
+          <t>37644</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>65777</t>
+          <t>65789</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>98690</t>
+          <t>99166</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>144957</t>
+          <t>144574</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,43%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>81937</t>
+          <t>80911</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>123876</t>
+          <t>123843</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5753,7 +5753,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>174513</t>
+          <t>175195</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>230319</t>
+          <t>230826</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>267406</t>
+          <t>270233</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>339998</t>
+          <t>338569</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>423766</t>
+          <t>423483</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>509059</t>
+          <t>511694</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>695421</t>
+          <t>698621</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>796332</t>
+          <t>799516</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1151428</t>
+          <t>1149000</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1278343</t>
+          <t>1279558</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,38%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1367373</t>
+          <t>1368953</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1484517</t>
+          <t>1479612</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>40,11%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>43,36%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1508202</t>
+          <t>1502340</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1629523</t>
+          <t>1625431</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>42,33%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2907389</t>
+          <t>2907014</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3083342</t>
+          <t>3072614</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>41,75%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>44,13%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>963952</t>
+          <t>963626</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1073221</t>
+          <t>1073192</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6092,7 +6092,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>745666</t>
+          <t>747465</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>848253</t>
+          <t>854805</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1741020</t>
+          <t>1753076</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1897454</t>
+          <t>1898354</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,27%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>362875</t>
+          <t>360051</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>439894</t>
+          <t>438043</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>206739</t>
+          <t>207383</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>268865</t>
+          <t>267697</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>588034</t>
+          <t>586881</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>687296</t>
+          <t>688484</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,89%</t>
         </is>
       </c>
     </row>
@@ -6651,12 +6651,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>37301</t>
+          <t>37520</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>64291</t>
+          <t>62846</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>95127</t>
+          <t>96412</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>137775</t>
+          <t>138540</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>141141</t>
+          <t>142141</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>192029</t>
+          <t>192340</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,02%</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>176133</t>
+          <t>177906</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>224244</t>
+          <t>225041</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>305502</t>
+          <t>308006</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>370616</t>
+          <t>367243</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>497290</t>
+          <t>493403</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>575735</t>
+          <t>574286</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>32,91%</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>250810</t>
+          <t>252399</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>301526</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>294729</t>
+          <t>292752</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>354922</t>
+          <t>357267</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>563683</t>
+          <t>562988</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>643274</t>
+          <t>642941</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>36,85%</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>140996</t>
+          <t>142578</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>187778</t>
+          <t>186125</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>137596</t>
+          <t>138895</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>185952</t>
+          <t>186750</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7040,12 +7040,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>290573</t>
+          <t>292142</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>354582</t>
+          <t>359285</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,59%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>52089</t>
+          <t>51675</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>82376</t>
+          <t>83156</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>40202</t>
+          <t>40867</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>68382</t>
+          <t>69106</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>96984</t>
+          <t>99032</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>139818</t>
+          <t>142521</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,17%</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24064</t>
+          <t>23668</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49297</t>
+          <t>49975</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7348,12 +7348,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>50251</t>
+          <t>50132</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>83600</t>
+          <t>82709</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>82085</t>
+          <t>81639</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>123738</t>
+          <t>123351</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>189870</t>
+          <t>188322</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>246665</t>
+          <t>244948</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>242135</t>
+          <t>240606</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>307985</t>
+          <t>307519</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>444722</t>
+          <t>443822</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>532998</t>
+          <t>534216</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,15%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>591265</t>
+          <t>593142</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>675206</t>
+          <t>680672</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>577100</t>
+          <t>578998</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>658633</t>
+          <t>664915</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1189105</t>
+          <t>1191267</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1310148</t>
+          <t>1305085</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,12%</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>754063</t>
+          <t>753566</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>841223</t>
+          <t>842398</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>36,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>650800</t>
+          <t>653660</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>737950</t>
+          <t>737648</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1430904</t>
+          <t>1439233</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1560372</t>
+          <t>1565342</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>38,53%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>358152</t>
+          <t>356818</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>427569</t>
+          <t>430875</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>305171</t>
+          <t>302129</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>370362</t>
+          <t>368410</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>678152</t>
+          <t>680526</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>772030</t>
+          <t>775309</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,08%</t>
         </is>
       </c>
     </row>
@@ -8015,12 +8015,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>1928</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12711</t>
+          <t>12306</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8030,12 +8030,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4421</t>
+          <t>4082</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17848</t>
+          <t>18454</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8094</t>
+          <t>8505</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25304</t>
+          <t>26880</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17203</t>
+          <t>16750</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>38824</t>
+          <t>38482</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8143,12 +8143,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>32294</t>
+          <t>33538</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>60637</t>
+          <t>59894</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>54948</t>
+          <t>55653</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>88475</t>
+          <t>91573</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,39%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>126277</t>
+          <t>125655</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>168307</t>
+          <t>167795</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>158950</t>
+          <t>159711</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>205258</t>
+          <t>206804</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>299862</t>
+          <t>297693</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>364051</t>
+          <t>362121</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,16%</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>214313</t>
+          <t>215039</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>264634</t>
+          <t>262725</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8369,12 +8369,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>194763</t>
+          <t>195357</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>240296</t>
+          <t>239051</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>421011</t>
+          <t>420512</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>485516</t>
+          <t>487422</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>44,63%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +8467,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>109326</t>
+          <t>108116</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>151093</t>
+          <t>150528</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8482,12 +8482,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>76289</t>
+          <t>76859</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>111089</t>
+          <t>113881</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8537,12 +8537,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>196369</t>
+          <t>195870</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>250921</t>
+          <t>249384</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8552,12 +8552,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,84%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>73280</t>
+          <t>73157</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>111659</t>
+          <t>113477</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>163663</t>
+          <t>164256</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>221466</t>
+          <t>221135</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8747,12 +8747,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>248438</t>
+          <t>247777</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>319120</t>
+          <t>318900</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8782,12 +8782,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>405120</t>
+          <t>404355</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>480651</t>
+          <t>483893</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>607513</t>
+          <t>602270</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>704058</t>
+          <t>701054</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1037517</t>
+          <t>1035216</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1157690</t>
+          <t>1158282</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,79%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1004425</t>
+          <t>999287</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1111582</t>
+          <t>1105996</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1066829</t>
+          <t>1077458</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1184544</t>
+          <t>1189586</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2104028</t>
+          <t>2089605</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2264844</t>
+          <t>2255478</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>32,69%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1149977</t>
+          <t>1140629</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1259612</t>
+          <t>1263031</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1022064</t>
+          <t>1015728</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1128602</t>
+          <t>1129643</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9086,12 +9086,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2193749</t>
+          <t>2191989</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2352482</t>
+          <t>2354304</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>34,12%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>545180</t>
+          <t>542415</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>633892</t>
+          <t>629462</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>444231</t>
+          <t>440689</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>527394</t>
+          <t>524118</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1009816</t>
+          <t>1004574</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1127075</t>
+          <t>1128081</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,35%</t>
         </is>
       </c>
     </row>
@@ -9605,32 +9605,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>55247</t>
+          <t>58755</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>44684</t>
+          <t>46838</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>69762</t>
+          <t>72966</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9640,32 +9640,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>119301</t>
+          <t>131129</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>106371</t>
+          <t>114056</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>135653</t>
+          <t>145424</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9675,32 +9675,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>174548</t>
+          <t>189884</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>155154</t>
+          <t>171324</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>193083</t>
+          <t>209265</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>14,94%</t>
         </is>
       </c>
     </row>
@@ -9718,32 +9718,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>149078</t>
+          <t>160659</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>131906</t>
+          <t>142822</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>169119</t>
+          <t>183013</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9753,32 +9753,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>274849</t>
+          <t>300891</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>254181</t>
+          <t>279763</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>295244</t>
+          <t>323503</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9788,32 +9788,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>423927</t>
+          <t>461550</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>396390</t>
+          <t>432503</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>453292</t>
+          <t>491085</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>35,06%</t>
         </is>
       </c>
     </row>
@@ -9831,32 +9831,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>206219</t>
+          <t>223863</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>184629</t>
+          <t>201252</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>225578</t>
+          <t>245376</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>42,41%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9866,32 +9866,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>275226</t>
+          <t>296612</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>254647</t>
+          <t>276447</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>296428</t>
+          <t>318021</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9901,32 +9901,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>481445</t>
+          <t>520475</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>452034</t>
+          <t>491618</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>512239</t>
+          <t>553240</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>39,5%</t>
         </is>
       </c>
     </row>
@@ -9944,32 +9944,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>70170</t>
+          <t>81416</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55558</t>
+          <t>65965</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>87597</t>
+          <t>99393</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9979,32 +9979,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>68276</t>
+          <t>75214</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>56272</t>
+          <t>62835</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>82293</t>
+          <t>89056</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10014,32 +10014,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>138446</t>
+          <t>156629</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>120719</t>
+          <t>135201</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>161449</t>
+          <t>178793</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,77%</t>
         </is>
       </c>
     </row>
@@ -10057,32 +10057,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>34224</t>
+          <t>53837</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>25216</t>
+          <t>38813</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>48725</t>
+          <t>74056</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10092,67 +10092,67 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>17855</t>
+          <t>18192</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10766</t>
+          <t>11364</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>29267</t>
+          <t>30772</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
+          <t>3,74%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>72028</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>54266</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>91979</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>5,14%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>3,87%</t>
         </is>
       </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>52079</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>38995</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>68782</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>4,1%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>3,07%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -10170,17 +10170,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10205,17 +10205,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10240,17 +10240,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10287,32 +10287,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>49703</t>
+          <t>51968</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32971</t>
+          <t>39312</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>64452</t>
+          <t>65174</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10322,32 +10322,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>50867</t>
+          <t>56497</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37389</t>
+          <t>45432</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>65007</t>
+          <t>68885</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10357,32 +10357,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>100570</t>
+          <t>108465</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>78499</t>
+          <t>91431</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>121682</t>
+          <t>126299</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -10400,32 +10400,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>246852</t>
+          <t>266581</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>169363</t>
+          <t>236189</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>291379</t>
+          <t>299242</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10435,32 +10435,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>304107</t>
+          <t>335015</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>221720</t>
+          <t>307290</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>351515</t>
+          <t>365641</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10470,32 +10470,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>550959</t>
+          <t>601596</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>447225</t>
+          <t>557290</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>621831</t>
+          <t>643347</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>14,62%</t>
         </is>
       </c>
     </row>
@@ -10513,69 +10513,69 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1069182</t>
+          <t>917153</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>906718</t>
+          <t>867441</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1477528</t>
+          <t>970243</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
+          <t>41,12%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>38,89%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>43,5%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1388</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>969987</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>929024</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>1013678</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>44,67%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>42,78%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
           <t>46,68%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>39,59%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>64,51%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>1388</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>1143340</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>999377</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>1431625</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>51,09%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>44,66%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>63,97%</t>
-        </is>
-      </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>2294</t>
@@ -10583,32 +10583,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>2212522</t>
+          <t>1887141</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1961961</t>
+          <t>1822567</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2692805</t>
+          <t>1954027</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>43,33%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>59,47%</t>
+          <t>44,39%</t>
         </is>
       </c>
     </row>
@@ -10626,32 +10626,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>654720</t>
+          <t>723437</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>431213</t>
+          <t>670959</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>750965</t>
+          <t>774100</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10661,32 +10661,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>554807</t>
+          <t>626963</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>416143</t>
+          <t>587665</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>636028</t>
+          <t>671884</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10696,32 +10696,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1209527</t>
+          <t>1350400</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>956603</t>
+          <t>1281310</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1344889</t>
+          <t>1415410</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>32,15%</t>
         </is>
       </c>
     </row>
@@ -10739,32 +10739,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>269870</t>
+          <t>271427</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>188442</t>
+          <t>231846</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>332447</t>
+          <t>318542</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10774,32 +10774,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>184703</t>
+          <t>182929</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>135096</t>
+          <t>153191</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>284268</t>
+          <t>213492</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10809,32 +10809,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>454573</t>
+          <t>454357</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>358555</t>
+          <t>407646</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>559238</t>
+          <t>504887</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>11,47%</t>
         </is>
       </c>
     </row>
@@ -10852,17 +10852,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10887,17 +10887,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10922,17 +10922,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10969,32 +10969,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>8901</t>
+          <t>10067</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4698</t>
+          <t>5125</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16170</t>
+          <t>18297</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11004,27 +11004,27 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>10706</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6635</t>
+          <t>7585</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16996</t>
+          <t>18903</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -11039,32 +11039,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>19608</t>
+          <t>22412</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13267</t>
+          <t>14862</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27591</t>
+          <t>30852</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -11082,32 +11082,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>59922</t>
+          <t>64367</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>46953</t>
+          <t>48724</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>75167</t>
+          <t>81037</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11117,32 +11117,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>58113</t>
+          <t>70625</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>46990</t>
+          <t>56770</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>71235</t>
+          <t>84173</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11152,32 +11152,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>118035</t>
+          <t>134992</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>102184</t>
+          <t>116651</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>139176</t>
+          <t>156501</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,82%</t>
         </is>
       </c>
     </row>
@@ -11195,32 +11195,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>301044</t>
+          <t>330604</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>274117</t>
+          <t>301808</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>330510</t>
+          <t>359751</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>46,46%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>42,41%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11230,32 +11230,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>298307</t>
+          <t>332820</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>273761</t>
+          <t>308239</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>320491</t>
+          <t>357480</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>45,29%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11265,32 +11265,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>599351</t>
+          <t>663424</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>562733</t>
+          <t>627793</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>635692</t>
+          <t>703031</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>45,85%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>43,4%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>48,6%</t>
         </is>
       </c>
     </row>
@@ -11308,32 +11308,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>187088</t>
+          <t>208948</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>163594</t>
+          <t>183235</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>215077</t>
+          <t>234719</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11343,32 +11343,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>210796</t>
+          <t>228114</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>187388</t>
+          <t>206480</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>232894</t>
+          <t>252755</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11378,32 +11378,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>397884</t>
+          <t>437063</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>366587</t>
+          <t>402727</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>431321</t>
+          <t>472324</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>32,65%</t>
         </is>
       </c>
     </row>
@@ -11421,32 +11421,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>89667</t>
+          <t>97601</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>67974</t>
+          <t>76736</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>120986</t>
+          <t>121473</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11456,32 +11456,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>82541</t>
+          <t>90972</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>67727</t>
+          <t>74961</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>99571</t>
+          <t>108995</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11491,32 +11491,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>172208</t>
+          <t>188573</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>145802</t>
+          <t>161960</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>208928</t>
+          <t>218398</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,1%</t>
         </is>
       </c>
     </row>
@@ -11534,17 +11534,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11569,17 +11569,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11604,17 +11604,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11651,32 +11651,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>113851</t>
+          <t>120790</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>88683</t>
+          <t>102707</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>135490</t>
+          <t>142633</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11686,32 +11686,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>180874</t>
+          <t>199971</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>147492</t>
+          <t>179408</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>205888</t>
+          <t>222454</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11721,32 +11721,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>294726</t>
+          <t>320761</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>253720</t>
+          <t>293579</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>330065</t>
+          <t>350550</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -11764,32 +11764,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>455853</t>
+          <t>491607</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>352489</t>
+          <t>455459</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>509755</t>
+          <t>535777</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11799,32 +11799,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>637069</t>
+          <t>706532</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>514274</t>
+          <t>667890</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>696138</t>
+          <t>747379</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11834,32 +11834,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1092922</t>
+          <t>1198139</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>941589</t>
+          <t>1138970</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1174982</t>
+          <t>1254815</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>17,31%</t>
         </is>
       </c>
     </row>
@@ -11877,32 +11877,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1576445</t>
+          <t>1471621</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1409485</t>
+          <t>1410180</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1984539</t>
+          <t>1535813</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11912,32 +11912,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1716873</t>
+          <t>1599419</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1568373</t>
+          <t>1548237</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2082068</t>
+          <t>1656061</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11947,32 +11947,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>3293318</t>
+          <t>3071040</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3026002</t>
+          <t>2989345</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3790847</t>
+          <t>3154869</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>43,52%</t>
         </is>
       </c>
     </row>
@@ -11990,32 +11990,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>911978</t>
+          <t>1013801</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>715138</t>
+          <t>954951</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1007801</t>
+          <t>1072258</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12025,32 +12025,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>833879</t>
+          <t>930291</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>667314</t>
+          <t>880157</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>913062</t>
+          <t>981073</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12060,32 +12060,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1745857</t>
+          <t>1944092</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1530731</t>
+          <t>1867386</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1885585</t>
+          <t>2026302</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>27,95%</t>
         </is>
       </c>
     </row>
@@ -12103,32 +12103,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>393761</t>
+          <t>422865</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>305779</t>
+          <t>373234</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>460729</t>
+          <t>476401</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12138,32 +12138,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>285098</t>
+          <t>292093</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>232195</t>
+          <t>257927</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>397222</t>
+          <t>324607</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12173,32 +12173,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>678860</t>
+          <t>714958</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>591998</t>
+          <t>657233</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>805378</t>
+          <t>776250</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>10,71%</t>
         </is>
       </c>
     </row>
@@ -12216,17 +12216,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12251,17 +12251,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12286,17 +12286,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
